--- a/Employee_Reports_wi52/Mark Jayson Rosima Q0265.xlsx
+++ b/Employee_Reports_wi52/Mark Jayson Rosima Q0265.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-77</v>
+        <v>-85</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-360</v>
+        <v>-368</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -971,11 +971,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-339</v>
+        <v>-347</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1020,11 +1020,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-443</v>
+        <v>-451</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1069,11 +1069,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-368</v>
+        <v>-376</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1106,11 +1106,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-368</v>
+        <v>-376</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1155,11 +1155,11 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
@@ -1170,41 +1170,41 @@
       <c r="K15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2024</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>25-Aug-2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1229,11 +1229,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
